--- a/整理后数据/2501/银行卡3001_2501.xlsx
+++ b/整理后数据/2501/银行卡3001_2501.xlsx
@@ -544,7 +544,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>示例银行C3001</t>
+          <t>示例银行C</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>示例银行C3001</t>
+          <t>示例银行C</t>
         </is>
       </c>
     </row>
